--- a/doc-anonymizer-v2/input/sample_document.xlsx
+++ b/doc-anonymizer-v2/input/sample_document.xlsx
@@ -429,8 +429,8 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -460,44 +460,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Bob Martinez</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>alice.johnson@acme.com</t>
+          <t>bob.martinez@acme.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(555) 234-5678</t>
+          <t>(555) 345-6789</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bob Martinez</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bob.martinez@acme.com</t>
+          <t>alice.johnson@acme.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(555) 345-6789</t>
+          <t>(555) 234-5678</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Bob Martinez</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bob Martinez</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>API key for test access: sk-a1b2c3d4e5f6g7h8. Contact: alice.johnson@acme.com</t>
+          <t>API key for staging access: sk-a1b2c3d4e5f6g7h8. Contact: bob.martinez@acme.com</t>
         </is>
       </c>
     </row>
